--- a/港岛-筲箕湾-One Eighty/One Eighty_销控明细表.xlsx
+++ b/港岛-筲箕湾-One Eighty/One Eighty_销控明细表.xlsx
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>14599800</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>43975</v>
+        <v>44108</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>12409830</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>37379</v>
+        <v>37492</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>10550700</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>31684</v>
+        <v>31779</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>8968095</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>26931</v>
+        <v>27012</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>10519350</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>31685</v>
+        <v>31781</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>8941448</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>26932</v>
+        <v>27013</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>10362600</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>31119</v>
+        <v>31213</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>8808210</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>26451</v>
+        <v>26531</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>10331250</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>31118</v>
+        <v>31212</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>8781562</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>26450</v>
+        <v>26530</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>10143150</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>30552</v>
+        <v>30644</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>8621678</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>25969</v>
+        <v>26047</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>9985450</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>29986</v>
+        <v>30077</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>8487632</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>25488</v>
+        <v>25565</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>9797350</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>29421</v>
+        <v>29510</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>8327748</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>25008</v>
+        <v>25084</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>4359900</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>26424</v>
+        <v>26585</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>4359900</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>26424</v>
+        <v>26585</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>6180300</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>24921</v>
+        <v>25021</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>6180300</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>24921</v>
+        <v>25021</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>6268000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>25274</v>
+        <v>25377</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>6268000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>25274</v>
+        <v>25377</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>3990900</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>24187</v>
+        <v>24335</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>3990900</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>24187</v>
+        <v>24335</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>5860500</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>23631</v>
+        <v>23727</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>5860500</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>23631</v>
+        <v>23727</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>3888400</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>23566</v>
+        <v>23710</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>3888400</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>23566</v>
+        <v>23710</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>5990900</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>24157</v>
+        <v>24255</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>5990900</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>24157</v>
+        <v>24255</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>4028700</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>24416</v>
+        <v>24565</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>4028700</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>24416</v>
+        <v>24565</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>5439000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>21931</v>
+        <v>22020</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>5439000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>21931</v>
+        <v>22020</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>3813000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>23109</v>
+        <v>23250</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>3813000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>23109</v>
+        <v>23250</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>5106100</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>20589</v>
+        <v>20672</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>5106100</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>20589</v>
+        <v>20672</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>3579300</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>21693</v>
+        <v>21825</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>3579300</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>21693</v>
+        <v>21825</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>5026600</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>20269</v>
+        <v>20351</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>5026600</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>20269</v>
+        <v>20351</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4392,9 +4392,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 332呎 (2房)
+          <t>A | 331呎 (2房)
 $1460万
-$43,975/呎
+$44,108/呎
 (在售)</t>
         </is>
       </c>
@@ -4464,17 +4464,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 332呎 (2房)
+          <t>A | 331呎 (2房)
 $1052万
-$31,685/呎
+$31,781/呎
 (在售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 333呎 (2房)
+          <t>B | 332呎 (2房)
 $1055万
-$31,684/呎
+$31,779/呎
 (在售)</t>
         </is>
       </c>
@@ -4488,17 +4488,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 332呎 (2房)
+          <t>A | 331呎 (2房)
 $1033万
-$31,118/呎
+$31,212/呎
 (在售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 333呎 (2房)
+          <t>B | 332呎 (2房)
 $1036万
-$31,119/呎
+$31,213/呎
 (在售)</t>
         </is>
       </c>
@@ -4512,9 +4512,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 332呎 (2房)
+          <t>A | 331呎 (2房)
 $1014万
-$30,552/呎
+$30,644/呎
 (在售)</t>
         </is>
       </c>
@@ -4544,9 +4544,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 333呎 (2房)
+          <t>B | 332呎 (2房)
 $999万
-$29,986/呎
+$30,077/呎
 (在售)</t>
         </is>
       </c>
@@ -4568,9 +4568,9 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 333呎 (2房)
+          <t>B | 332呎 (2房)
 $980万
-$29,421/呎
+$29,510/呎
 (在售)</t>
         </is>
       </c>
@@ -4592,9 +4592,9 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 165呎 (开放式)
+          <t>B | 164呎 (开放式)
 $436万
-$26,424/呎
+$26,585/呎
 (19年-11月-29日)</t>
         </is>
       </c>
@@ -4631,9 +4631,9 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $618万
-$24,921/呎
+$25,021/呎
 (19年-11月-26日)</t>
         </is>
       </c>
@@ -4662,9 +4662,9 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $627万
-$25,274/呎
+$25,377/呎
 (19年-11月-26日)</t>
         </is>
       </c>
@@ -4685,9 +4685,9 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>B | 165呎 (开放式)
+          <t>B | 164呎 (开放式)
 $399万
-$24,187/呎
+$24,335/呎
 (19年-11月-28日)</t>
         </is>
       </c>
@@ -4724,9 +4724,9 @@
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $586万
-$23,631/呎
+$23,727/呎
 (19年-11月-29日)</t>
         </is>
       </c>
@@ -4747,9 +4747,9 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>B | 165呎 (开放式)
+          <t>B | 164呎 (开放式)
 $389万
-$23,566/呎
+$23,710/呎
 (19年-11月-27日)</t>
         </is>
       </c>
@@ -4778,17 +4778,17 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>B | 165呎 (开放式)
+          <t>B | 164呎 (开放式)
 $403万
-$24,416/呎
+$24,565/呎
 (20年-07月-03日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $599万
-$24,157/呎
+$24,255/呎
 (19年-11月-27日)</t>
         </is>
       </c>
@@ -4902,17 +4902,17 @@
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>B | 165呎 (开放式)
+          <t>B | 164呎 (开放式)
 $381万
-$23,109/呎
+$23,250/呎
 (19年-11月-27日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $544万
-$21,931/呎
+$22,020/呎
 (19年-11月-25日)</t>
         </is>
       </c>
@@ -4933,17 +4933,17 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>B | 165呎 (开放式)
+          <t>B | 164呎 (开放式)
 $358万
-$21,693/呎
+$21,825/呎
 (19年-11月-22日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $511万
-$20,589/呎
+$20,672/呎
 (19年-11月-22日)</t>
         </is>
       </c>
@@ -4972,9 +4972,9 @@
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>C | 248呎 (1房)
+          <t>C | 247呎 (1房)
 $503万
-$20,269/呎
+$20,351/呎
 (19年-11月-22日)</t>
         </is>
       </c>
